--- a/ПРАКТИКА инфор.технологии/Практика 4.xlsx
+++ b/ПРАКТИКА инфор.технологии/Практика 4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxpr\OneDrive\Рабочий стол\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Second_year_of_college\ПРАКТИКА инфор.технологии\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0EB223-CE3C-4997-BFC1-69A52AFD1806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DC509C-F1CE-499D-9FEE-ACE73D815D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4170" yWindow="0" windowWidth="21600" windowHeight="11850" activeTab="6" xr2:uid="{E7EA0BB0-0619-4C7F-9614-504D087F3756}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{E7EA0BB0-0619-4C7F-9614-504D087F3756}"/>
   </bookViews>
   <sheets>
     <sheet name="Закупки" sheetId="1" r:id="rId1"/>
@@ -282,7 +282,7 @@
     <numFmt numFmtId="164" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     <numFmt numFmtId="165" formatCode="[$$-409]#,##0.00"/>
     <numFmt numFmtId="166" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="168" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -794,7 +794,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -894,18 +894,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -915,11 +903,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -951,10 +936,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -967,16 +951,15 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1001,6 +984,24 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1008,42 +1009,34 @@
   <dxfs count="18">
     <dxf>
       <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
         <color auto="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="medium">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="medium">
-          <color auto="1"/>
-        </horizontal>
-      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAF6901"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1133,13 +1126,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color auto="1"/>
@@ -1178,35 +1164,50 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
         <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFAF6901"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="medium">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="medium">
+          <color auto="1"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1279,6 +1280,44 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="medium">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -1311,44 +1350,6 @@
         </right>
         <top/>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="medium">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="medium">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
@@ -6245,7 +6246,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DA802BC4-38A5-4B5B-8A97-92F794F98570}" name="Таблица1" displayName="Таблица1" ref="H2:I6" totalsRowShown="0" headerRowDxfId="13" dataDxfId="14" headerRowBorderDxfId="16" tableBorderDxfId="17" totalsRowBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DA802BC4-38A5-4B5B-8A97-92F794F98570}" name="Таблица1" displayName="Таблица1" ref="H2:I6" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
   <autoFilter ref="H2:I6" xr:uid="{DA802BC4-38A5-4B5B-8A97-92F794F98570}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{E033EB28-C6CE-4348-BEC9-67A97A5EFB76}" name="Фамилия" dataDxfId="12"/>
@@ -6256,11 +6257,11 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{62FDA9C8-B74D-4FD5-926A-89E65D90DA4B}" name="Таблица2" displayName="Таблица2" ref="H8:I11" totalsRowShown="0" headerRowDxfId="0" dataDxfId="6" headerRowBorderDxfId="4" tableBorderDxfId="5" totalsRowBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{62FDA9C8-B74D-4FD5-926A-89E65D90DA4B}" name="Таблица2" displayName="Таблица2" ref="H8:I11" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
   <autoFilter ref="H8:I11" xr:uid="{62FDA9C8-B74D-4FD5-926A-89E65D90DA4B}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{932BCDD8-81F8-43F6-94A6-D681849DD73A}" name="Месяц" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{15AE40AC-1B66-433D-9AF9-85BDD4504836}" name="Сумма пособий" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{932BCDD8-81F8-43F6-94A6-D681849DD73A}" name="Месяц" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{15AE40AC-1B66-433D-9AF9-85BDD4504836}" name="Сумма пособий" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6576,15 +6577,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="35.25" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
@@ -6811,13 +6812,13 @@
     </row>
     <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:9" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="43"/>
+      <c r="B11" s="78"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="78"/>
+      <c r="E11" s="79"/>
       <c r="G11" s="19">
         <f>SUM(E3:E9)</f>
         <v>17873.480000000003</v>
@@ -6832,13 +6833,13 @@
       <c r="G12" s="20"/>
     </row>
     <row r="13" spans="1:9" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="43"/>
+      <c r="B13" s="78"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="79"/>
       <c r="G13" s="21">
         <f>SUM(G3:G9)</f>
         <v>1456152.4156000002</v>
@@ -6853,13 +6854,13 @@
       <c r="G14" s="20"/>
     </row>
     <row r="15" spans="1:9" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="43"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="78"/>
+      <c r="D15" s="78"/>
+      <c r="E15" s="79"/>
       <c r="G15" s="21">
         <f>AVERAGE(G3:G9)</f>
         <v>208021.77365714288</v>
@@ -6874,13 +6875,13 @@
       <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="43"/>
+      <c r="B17" s="78"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="79"/>
       <c r="G17" s="21">
         <f>MAX(G3:G9)</f>
         <v>993934</v>
@@ -6895,13 +6896,13 @@
       <c r="G18" s="20"/>
     </row>
     <row r="19" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="41" t="s">
+      <c r="A19" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="43"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="78"/>
+      <c r="D19" s="78"/>
+      <c r="E19" s="79"/>
       <c r="G19" s="19">
         <f>MAX(E3:E9)</f>
         <v>12200</v>
@@ -6916,13 +6917,13 @@
       <c r="G20" s="22"/>
     </row>
     <row r="21" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="41" t="s">
+      <c r="A21" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="42"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="43"/>
+      <c r="B21" s="78"/>
+      <c r="C21" s="78"/>
+      <c r="D21" s="78"/>
+      <c r="E21" s="79"/>
       <c r="G21" s="23">
         <v>81.47</v>
       </c>
@@ -7409,31 +7410,31 @@
       </c>
       <c r="D2" s="35">
         <f ca="1">RANDBETWEEN(1, 100)</f>
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E2" s="35">
         <f t="shared" ref="E2:J11" ca="1" si="0">RANDBETWEEN(1, 100)</f>
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F2" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G2" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="H2" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="I2" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="J2" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7448,31 +7449,31 @@
       </c>
       <c r="D3" s="35">
         <f t="shared" ref="D3:D11" ca="1" si="1">RANDBETWEEN(1, 100)</f>
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E3" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="F3" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="G3" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="H3" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I3" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J3" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7487,31 +7488,31 @@
       </c>
       <c r="D4" s="35">
         <f t="shared" ca="1" si="1"/>
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="E4" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="F4" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="G4" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="H4" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="I4" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="J4" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7526,31 +7527,31 @@
       </c>
       <c r="D5" s="35">
         <f t="shared" ca="1" si="1"/>
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E5" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F5" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G5" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="H5" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="I5" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="J5" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7565,31 +7566,31 @@
       </c>
       <c r="D6" s="35">
         <f t="shared" ca="1" si="1"/>
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="E6" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F6" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="G6" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="H6" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="I6" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>93</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7604,31 +7605,31 @@
       </c>
       <c r="D7" s="35">
         <f t="shared" ca="1" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="E7" s="35">
+        <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
-      <c r="E7" s="35">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
       <c r="F7" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>92</v>
+        <v>7</v>
       </c>
       <c r="G7" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="H7" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="I7" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>58</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7643,31 +7644,31 @@
       </c>
       <c r="D8" s="35">
         <f t="shared" ca="1" si="1"/>
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="E8" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="F8" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="G8" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="H8" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="I8" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>79</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7682,31 +7683,31 @@
       </c>
       <c r="D9" s="35">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="E9" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="F9" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G9" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H9" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="I9" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J9" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7721,31 +7722,31 @@
       </c>
       <c r="D10" s="35">
         <f t="shared" ca="1" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="E10" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="F10" s="35">
+        <f t="shared" ca="1" si="0"/>
         <v>98</v>
       </c>
-      <c r="E10" s="35">
-        <f t="shared" ca="1" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="F10" s="35">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
       <c r="G10" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="H10" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="I10" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7760,47 +7761,47 @@
       </c>
       <c r="D11" s="37">
         <f t="shared" ca="1" si="1"/>
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="E11" s="37">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="F11" s="37">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="G11" s="37">
         <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H11" s="37">
         <f t="shared" ca="1" si="0"/>
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="I11" s="37">
         <f t="shared" ca="1" si="0"/>
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="J11" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>62</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="D2:J11">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
       <formula>51</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
       <formula>86</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="between">
       <formula>71</formula>
       <formula>85</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="between">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="between">
       <formula>51</formula>
       <formula>70</formula>
     </cfRule>
@@ -7814,13 +7815,13 @@
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="40">
         <f ca="1">TODAY()</f>
-        <v>45973</v>
+        <v>45985</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -7832,13 +7833,13 @@
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="18">
         <f ca="1">DAY(TODAY())</f>
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="str">
         <f ca="1">TEXT(TODAY(),"ДДДД")</f>
-        <v>среда</v>
+        <v>понедельник</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -7847,15 +7848,15 @@
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18">
-        <f ca="1">YEAR(TODAY()) - YEAR(A5)</f>
+      <c r="A6" s="82">
+        <f ca="1">DATEDIF(A5, A1, "y")</f>
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="40">
         <f ca="1">NOW()</f>
-        <v>45973.059380787039</v>
+        <v>45985.393178587961</v>
       </c>
     </row>
   </sheetData>
@@ -7875,7 +7876,7 @@
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="39">
         <f ca="1">NOW()</f>
-        <v>45973.059380787039</v>
+        <v>45985.393178587961</v>
       </c>
       <c r="B1" s="39" t="str">
         <f ca="1" xml:space="preserve"> IF(TIME(13,0,0)&lt;=A1&lt;=TIME(14,0,0),"Обед","Работаем")</f>
@@ -7902,324 +7903,324 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="46" t="s">
+      <c r="E1" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="47" t="s">
+      <c r="G1" s="43" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="49">
+      <c r="A2" s="44">
         <v>1</v>
       </c>
-      <c r="B2" s="51">
+      <c r="B2" s="46">
         <f ca="1">RANDBETWEEN(2,5)</f>
-        <v>4</v>
-      </c>
-      <c r="C2" s="51">
+        <v>2</v>
+      </c>
+      <c r="C2" s="46">
         <f t="shared" ref="C2:E11" ca="1" si="0">RANDBETWEEN(2,5)</f>
-        <v>4</v>
-      </c>
-      <c r="D2" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="E2" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="F2" s="51">
+        <v>2</v>
+      </c>
+      <c r="D2" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E2" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="F2" s="46">
         <f ca="1">B2+C2+D2+E2</f>
-        <v>16</v>
-      </c>
-      <c r="G2" s="50" t="str">
+        <v>8</v>
+      </c>
+      <c r="G2" s="45" t="str">
         <f ca="1">IF(AND(C2&gt;=4,F2&gt;=$E$12),"да","нет")</f>
-        <v>да</v>
+        <v>нет</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="49">
+      <c r="A3" s="44">
         <v>2</v>
       </c>
-      <c r="B3" s="51">
+      <c r="B3" s="46">
         <f t="shared" ref="B3:B11" ca="1" si="1">RANDBETWEEN(2,5)</f>
-        <v>2</v>
-      </c>
-      <c r="C3" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="D3" s="51">
-        <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="E3" s="51">
+      <c r="C3" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="D3" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E3" s="46">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="F3" s="51">
+      <c r="F3" s="46">
         <f t="shared" ref="F3:F11" ca="1" si="2">B3+C3+D3+E3</f>
-        <v>14</v>
-      </c>
-      <c r="G3" s="50" t="str">
+        <v>13</v>
+      </c>
+      <c r="G3" s="45" t="str">
         <f t="shared" ref="G3:G11" ca="1" si="3">IF(AND(C3&gt;=4,F3&gt;=$E$12),"да","нет")</f>
-        <v>да</v>
+        <v>нет</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="49">
+      <c r="A4" s="44">
         <v>3</v>
       </c>
-      <c r="B4" s="51">
+      <c r="B4" s="46">
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="C4" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D4" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E4" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F4" s="46">
+        <f t="shared" ca="1" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="G4" s="45" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>нет</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="44">
+        <v>4</v>
+      </c>
+      <c r="B5" s="46">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="C5" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D5" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="E5" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F5" s="46">
+        <f t="shared" ca="1" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="G5" s="45" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>да</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="44">
+        <v>5</v>
+      </c>
+      <c r="B6" s="46">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="C6" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D6" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="E6" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F6" s="46">
+        <f t="shared" ca="1" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="G6" s="45" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>да</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="44">
+        <v>6</v>
+      </c>
+      <c r="B7" s="46">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="C7" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D7" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E7" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="F7" s="46">
+        <f t="shared" ca="1" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="G7" s="45" t="str">
+        <f ca="1">IF(AND(C7&gt;=4,F7&gt;=$E$12),"да","нет")</f>
+        <v>нет</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="44">
+        <v>7</v>
+      </c>
+      <c r="B8" s="46">
+        <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="C8" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D8" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E8" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F8" s="46">
+        <f t="shared" ca="1" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="G8" s="45" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>да</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="44">
+        <v>8</v>
+      </c>
+      <c r="B9" s="46">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
-      <c r="C4" s="51">
+      <c r="C9" s="46">
         <f t="shared" ca="1" si="0"/>
         <v>5</v>
       </c>
-      <c r="D4" s="51">
-        <f t="shared" ca="1" si="0"/>
+      <c r="D9" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E9" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F9" s="46">
+        <f t="shared" ca="1" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="G9" s="45" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>да</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="44">
+        <v>9</v>
+      </c>
+      <c r="B10" s="46">
+        <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
-      <c r="E4" s="51">
+      <c r="C10" s="46">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="F4" s="51">
+      <c r="D10" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E10" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F10" s="46">
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="G10" s="45" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>да</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="44">
+        <v>10</v>
+      </c>
+      <c r="B11" s="46">
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="C11" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="D11" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E11" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F11" s="46">
         <f t="shared" ca="1" si="2"/>
         <v>13</v>
       </c>
-      <c r="G4" s="50" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>да</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="49">
-        <v>4</v>
-      </c>
-      <c r="B5" s="51">
-        <f t="shared" ca="1" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="C5" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D5" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="E5" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="F5" s="51">
-        <f t="shared" ca="1" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="G5" s="50" t="str">
+      <c r="G11" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>нет</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="49">
-        <v>5</v>
-      </c>
-      <c r="B6" s="51">
-        <f t="shared" ca="1" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="C6" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D6" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="E6" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="F6" s="51">
-        <f t="shared" ca="1" si="2"/>
-        <v>14</v>
-      </c>
-      <c r="G6" s="50" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>нет</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="49">
-        <v>6</v>
-      </c>
-      <c r="B7" s="51">
-        <f t="shared" ca="1" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="C7" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D7" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="E7" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="F7" s="51">
-        <f t="shared" ca="1" si="2"/>
-        <v>13</v>
-      </c>
-      <c r="G7" s="50" t="str">
-        <f ca="1">IF(AND(C7&gt;=4,F7&gt;=$E$12),"да","нет")</f>
-        <v>нет</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="49">
-        <v>7</v>
-      </c>
-      <c r="B8" s="51">
-        <f t="shared" ca="1" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="C8" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="D8" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="E8" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="F8" s="51">
-        <f t="shared" ca="1" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="G8" s="50" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>нет</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="49">
-        <v>8</v>
-      </c>
-      <c r="B9" s="51">
-        <f t="shared" ca="1" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="C9" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="D9" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="E9" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="F9" s="51">
-        <f t="shared" ca="1" si="2"/>
-        <v>18</v>
-      </c>
-      <c r="G9" s="50" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>да</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="49">
-        <v>9</v>
-      </c>
-      <c r="B10" s="51">
-        <f t="shared" ca="1" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="C10" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="D10" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="E10" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="F10" s="51">
-        <f t="shared" ca="1" si="2"/>
-        <v>16</v>
-      </c>
-      <c r="G10" s="50" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>нет</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="49">
-        <v>10</v>
-      </c>
-      <c r="B11" s="51">
-        <f t="shared" ca="1" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="C11" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D11" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="E11" s="51">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="F11" s="51">
-        <f t="shared" ca="1" si="2"/>
-        <v>13</v>
-      </c>
-      <c r="G11" s="50" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>нет</v>
-      </c>
-    </row>
     <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="81" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="48"/>
-      <c r="E12" s="45">
+      <c r="D12" s="81"/>
+      <c r="E12" s="41">
         <v>13</v>
       </c>
     </row>
@@ -8249,349 +8250,347 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="D1" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="62" t="s">
+      <c r="E1" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="70"/>
-      <c r="I1" s="71"/>
+      <c r="H1" s="64"/>
     </row>
     <row r="2" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="52">
+      <c r="A2" s="47">
         <v>1</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="54">
+      <c r="C2" s="49">
         <v>45385</v>
       </c>
-      <c r="D2" s="64">
+      <c r="D2" s="58">
         <f>MONTH(C2)</f>
         <v>4</v>
       </c>
-      <c r="E2" s="65">
+      <c r="E2" s="59">
         <f ca="1">(TODAY() - C2 )/365</f>
-        <v>1.6109589041095891</v>
-      </c>
-      <c r="F2" s="69">
-        <f ca="1">_xlfn.IFS(E2&lt;=3,$E$14,E2&lt;=8,$E$14*0.8,E2&lt;=17,$E$14*0.6,E2&gt;17,"нет")</f>
+        <v>1.6438356164383561</v>
+      </c>
+      <c r="F2" s="63">
+        <f t="shared" ref="F2:F11" ca="1" si="0">_xlfn.IFS(E2&lt;=3,$E$14,E2&lt;=8,$E$14*0.8,E2&lt;=17,$E$14*0.6,E2&gt;17,"нет")</f>
         <v>12345.78</v>
       </c>
-      <c r="G2" s="63"/>
-      <c r="H2" s="74" t="s">
+      <c r="H2" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="68" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="55">
+      <c r="A3" s="50">
         <v>2</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="57">
+      <c r="C3" s="52">
         <v>44666</v>
       </c>
-      <c r="D3" s="64">
-        <f t="shared" ref="D3:D11" si="0">MONTH(C3)</f>
+      <c r="D3" s="58">
+        <f t="shared" ref="D3:D11" si="1">MONTH(C3)</f>
         <v>4</v>
       </c>
-      <c r="E3" s="65">
-        <f t="shared" ref="E3:E11" ca="1" si="1">(TODAY() - C3 )/365.25</f>
-        <v>3.5783709787816562</v>
-      </c>
-      <c r="F3" s="69">
-        <f ca="1">_xlfn.IFS(E3&lt;=3,$E$14,E3&lt;=8,$E$14*0.8,E3&lt;=17,$E$14*0.6,E3&gt;17,"нет")</f>
+      <c r="E3" s="59">
+        <f t="shared" ref="E3:E11" ca="1" si="2">(TODAY() - C3 )/365.25</f>
+        <v>3.6112251882272415</v>
+      </c>
+      <c r="F3" s="63">
+        <f t="shared" ca="1" si="0"/>
         <v>9876.6240000000016</v>
       </c>
-      <c r="H3" s="72" t="s">
+      <c r="H3" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="I3" s="76">
+      <c r="I3" s="69">
         <f ca="1">SUMIF(B2:B11,"Иванов*",F2:F11)</f>
         <v>27160.716</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="55">
+      <c r="A4" s="50">
         <v>3</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="57">
+      <c r="C4" s="52">
         <v>43565</v>
       </c>
-      <c r="D4" s="64">
-        <f t="shared" si="0"/>
+      <c r="D4" s="58">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="E4" s="65">
-        <f t="shared" ca="1" si="1"/>
-        <v>6.5927446954141002</v>
-      </c>
-      <c r="F4" s="69">
-        <f ca="1">_xlfn.IFS(E4&lt;=3,$E$14,E4&lt;=8,$E$14*0.8,E4&lt;=17,$E$14*0.6,E4&gt;17,"нет")</f>
+      <c r="E4" s="59">
+        <f t="shared" ca="1" si="2"/>
+        <v>6.6255989048596851</v>
+      </c>
+      <c r="F4" s="63">
+        <f t="shared" ca="1" si="0"/>
         <v>9876.6240000000016</v>
       </c>
-      <c r="H4" s="72" t="s">
+      <c r="H4" s="65" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="76">
+      <c r="I4" s="69">
         <f ca="1">SUMIF(B2:B11,"Лебедева*",F2:F11)</f>
         <v>17284.092000000001</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="52">
+      <c r="A5" s="47">
         <v>4</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="57">
+      <c r="C5" s="52">
         <v>42877</v>
       </c>
-      <c r="D5" s="64">
-        <f t="shared" si="0"/>
+      <c r="D5" s="58">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="E5" s="65">
-        <f t="shared" ca="1" si="1"/>
-        <v>8.4763860369609851</v>
-      </c>
-      <c r="F5" s="69">
-        <f ca="1">_xlfn.IFS(E5&lt;=3,$E$14,E5&lt;=8,$E$14*0.8,E5&lt;=17,$E$14*0.6,E5&gt;17,"нет")</f>
+      <c r="E5" s="59">
+        <f t="shared" ca="1" si="2"/>
+        <v>8.5092402464065717</v>
+      </c>
+      <c r="F5" s="63">
+        <f t="shared" ca="1" si="0"/>
         <v>7407.4679999999998</v>
       </c>
-      <c r="H5" s="72" t="s">
+      <c r="H5" s="65" t="s">
         <v>73</v>
       </c>
-      <c r="I5" s="76">
+      <c r="I5" s="69">
         <f ca="1">SUMIF(B2:B11,"Сидоров*",F2:F11)</f>
         <v>17284.092000000001</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="55">
+      <c r="A6" s="50">
         <v>5</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="57">
+      <c r="C6" s="52">
         <v>42129</v>
       </c>
-      <c r="D6" s="64">
-        <f t="shared" si="0"/>
+      <c r="D6" s="58">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="E6" s="65">
-        <f t="shared" ca="1" si="1"/>
-        <v>10.524298425735797</v>
-      </c>
-      <c r="F6" s="69">
-        <f ca="1">_xlfn.IFS(E6&lt;=3,$E$14,E6&lt;=8,$E$14*0.8,E6&lt;=17,$E$14*0.6,E6&gt;17,"нет")</f>
+      <c r="E6" s="59">
+        <f t="shared" ca="1" si="2"/>
+        <v>10.557152635181383</v>
+      </c>
+      <c r="F6" s="63">
+        <f t="shared" ca="1" si="0"/>
         <v>7407.4679999999998</v>
       </c>
-      <c r="H6" s="73" t="s">
+      <c r="H6" s="66" t="s">
         <v>74</v>
       </c>
-      <c r="I6" s="77">
+      <c r="I6" s="70">
         <f ca="1">SUMIF(B2:B11,"Федорова*",F2:F11)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="55">
+      <c r="A7" s="50">
         <v>6</v>
       </c>
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="57">
+      <c r="C7" s="52">
         <v>40693</v>
       </c>
-      <c r="D7" s="64">
-        <f t="shared" si="0"/>
+      <c r="D7" s="58">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="E7" s="65">
-        <f t="shared" ca="1" si="1"/>
-        <v>14.455852156057494</v>
-      </c>
-      <c r="F7" s="69">
-        <f ca="1">_xlfn.IFS(E7&lt;=3,$E$14,E7&lt;=8,$E$14*0.8,E7&lt;=17,$E$14*0.6,E7&gt;17,"нет")</f>
+      <c r="E7" s="59">
+        <f t="shared" ca="1" si="2"/>
+        <v>14.488706365503081</v>
+      </c>
+      <c r="F7" s="63">
+        <f t="shared" ca="1" si="0"/>
         <v>7407.4679999999998</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="52">
+      <c r="A8" s="47">
         <v>7</v>
       </c>
-      <c r="B8" s="59" t="s">
+      <c r="B8" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="57">
+      <c r="C8" s="52">
         <v>39858</v>
       </c>
-      <c r="D8" s="64">
-        <f t="shared" si="0"/>
+      <c r="D8" s="58">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="E8" s="65">
-        <f t="shared" ca="1" si="1"/>
-        <v>16.741957563312798</v>
-      </c>
-      <c r="F8" s="69">
-        <f ca="1">_xlfn.IFS(E8&lt;=3,$E$14,E8&lt;=8,$E$14*0.8,E8&lt;=17,$E$14*0.6,E8&gt;17,"нет")</f>
+      <c r="E8" s="59">
+        <f t="shared" ca="1" si="2"/>
+        <v>16.774811772758383</v>
+      </c>
+      <c r="F8" s="63">
+        <f t="shared" ca="1" si="0"/>
         <v>7407.4679999999998</v>
       </c>
-      <c r="H8" s="78" t="s">
+      <c r="H8" s="71" t="s">
         <v>71</v>
       </c>
-      <c r="I8" s="79" t="s">
+      <c r="I8" s="72" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="55">
+      <c r="A9" s="50">
         <v>8</v>
       </c>
-      <c r="B9" s="59" t="s">
+      <c r="B9" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="57">
+      <c r="C9" s="52">
         <v>39496</v>
       </c>
-      <c r="D9" s="64">
-        <f t="shared" si="0"/>
+      <c r="D9" s="58">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="E9" s="65">
-        <f t="shared" ca="1" si="1"/>
-        <v>17.733059548254619</v>
-      </c>
-      <c r="F9" s="69" t="str">
-        <f ca="1">_xlfn.IFS(E9&lt;=3,$E$14,E9&lt;=8,$E$14*0.8,E9&lt;=17,$E$14*0.6,E9&gt;17,"нет")</f>
+      <c r="E9" s="59">
+        <f t="shared" ca="1" si="2"/>
+        <v>17.765913757700204</v>
+      </c>
+      <c r="F9" s="63" t="str">
+        <f t="shared" ca="1" si="0"/>
         <v>нет</v>
       </c>
-      <c r="H9" s="80" t="s">
+      <c r="H9" s="73" t="s">
         <v>77</v>
       </c>
-      <c r="I9" s="81">
+      <c r="I9" s="74">
         <f ca="1">SUMIF(D2:D11,"4",F2:F11)</f>
         <v>32099.028000000006</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="55">
+      <c r="A10" s="50">
         <v>9</v>
       </c>
-      <c r="B10" s="59" t="s">
+      <c r="B10" s="54" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="57">
+      <c r="C10" s="52">
         <v>38773</v>
       </c>
-      <c r="D10" s="64">
-        <f t="shared" si="0"/>
+      <c r="D10" s="58">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="E10" s="65">
-        <f t="shared" ca="1" si="1"/>
-        <v>19.71252566735113</v>
-      </c>
-      <c r="F10" s="69" t="str">
-        <f ca="1">_xlfn.IFS(E10&lt;=3,$E$14,E10&lt;=8,$E$14*0.8,E10&lt;=17,$E$14*0.6,E10&gt;17,"нет")</f>
+      <c r="E10" s="59">
+        <f t="shared" ca="1" si="2"/>
+        <v>19.745379876796715</v>
+      </c>
+      <c r="F10" s="63" t="str">
+        <f t="shared" ca="1" si="0"/>
         <v>нет</v>
       </c>
-      <c r="H10" s="80" t="s">
+      <c r="H10" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="I10" s="81">
+      <c r="I10" s="74">
         <f ca="1">SUMIF(D2:D11,"5",F2:F11)</f>
         <v>22222.403999999999</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="52">
+      <c r="A11" s="47">
         <v>10</v>
       </c>
-      <c r="B11" s="59" t="s">
+      <c r="B11" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="57">
+      <c r="C11" s="52">
         <v>38026</v>
       </c>
-      <c r="D11" s="64">
-        <f t="shared" si="0"/>
+      <c r="D11" s="58">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="E11" s="65">
-        <f t="shared" ca="1" si="1"/>
-        <v>21.757700205338811</v>
-      </c>
-      <c r="F11" s="69" t="str">
-        <f ca="1">_xlfn.IFS(E11&lt;=3,$E$14,E11&lt;=8,$E$14*0.8,E11&lt;=17,$E$14*0.6,E11&gt;17,"нет")</f>
+      <c r="E11" s="59">
+        <f t="shared" ca="1" si="2"/>
+        <v>21.790554414784395</v>
+      </c>
+      <c r="F11" s="63" t="str">
+        <f t="shared" ca="1" si="0"/>
         <v>нет</v>
       </c>
-      <c r="H11" s="82" t="s">
+      <c r="H11" s="75" t="s">
         <v>79</v>
       </c>
-      <c r="I11" s="83">
+      <c r="I11" s="76">
         <f ca="1">SUMIF(D2:D11,"2",F2:F11)</f>
         <v>7407.4679999999998</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="66" t="s">
+      <c r="B13" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="69">
+      <c r="C13" s="63">
         <f ca="1">SUM(F2:F11)</f>
         <v>61728.900000000009</v>
       </c>
-      <c r="E13" s="60" t="s">
+      <c r="E13" s="55" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="66" t="s">
+      <c r="B14" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="67">
+      <c r="C14" s="61">
         <f ca="1">AVERAGE(E2:E11)</f>
-        <v>12.118385418131698</v>
-      </c>
-      <c r="E14" s="68">
+        <v>12.151241877865601</v>
+      </c>
+      <c r="E14" s="62">
         <v>12345.78</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="66" t="s">
+      <c r="B15" s="60" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="64">
+      <c r="C15" s="58">
         <f ca="1">COUNTIF(E2:E11,"&gt;8")</f>
         <v>7</v>
       </c>

--- a/ПРАКТИКА инфор.технологии/Практика 4.xlsx
+++ b/ПРАКТИКА инфор.технологии/Практика 4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Second_year_of_college\ПРАКТИКА инфор.технологии\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DC509C-F1CE-499D-9FEE-ACE73D815D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{697F2FBA-9C3F-4DA4-AF2D-612BB874D0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{E7EA0BB0-0619-4C7F-9614-504D087F3756}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="6" xr2:uid="{E7EA0BB0-0619-4C7F-9614-504D087F3756}"/>
   </bookViews>
   <sheets>
     <sheet name="Закупки" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -984,6 +995,9 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -999,14 +1013,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="22">
     <dxf>
       <font>
         <color auto="1"/>
@@ -1028,6 +1039,37 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAF6901"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6246,31 +6288,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DA802BC4-38A5-4B5B-8A97-92F794F98570}" name="Таблица1" displayName="Таблица1" ref="H2:I6" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DA802BC4-38A5-4B5B-8A97-92F794F98570}" name="Таблица1" displayName="Таблица1" ref="H2:I6" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18" totalsRowBorderDxfId="17">
   <autoFilter ref="H2:I6" xr:uid="{DA802BC4-38A5-4B5B-8A97-92F794F98570}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E033EB28-C6CE-4348-BEC9-67A97A5EFB76}" name="Фамилия" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{9776BFA0-FA03-4950-A707-383453F25CBB}" name="Сумма пособий" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{E033EB28-C6CE-4348-BEC9-67A97A5EFB76}" name="Фамилия" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{9776BFA0-FA03-4950-A707-383453F25CBB}" name="Сумма пособий" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{62FDA9C8-B74D-4FD5-926A-89E65D90DA4B}" name="Таблица2" displayName="Таблица2" ref="H8:I11" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{62FDA9C8-B74D-4FD5-926A-89E65D90DA4B}" name="Таблица2" displayName="Таблица2" ref="H8:I11" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="H8:I11" xr:uid="{62FDA9C8-B74D-4FD5-926A-89E65D90DA4B}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{932BCDD8-81F8-43F6-94A6-D681849DD73A}" name="Месяц" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{15AE40AC-1B66-433D-9AF9-85BDD4504836}" name="Сумма пособий" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{932BCDD8-81F8-43F6-94A6-D681849DD73A}" name="Месяц" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{15AE40AC-1B66-433D-9AF9-85BDD4504836}" name="Сумма пособий" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6308,7 +6350,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6414,7 +6456,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6556,7 +6598,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6565,31 +6607,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A139641-B2FE-4628-B8CB-3A90CAD6BB04}">
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="35.25" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="80" t="s">
+    <row r="1" spans="1:9" ht="35.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="70.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -6614,7 +6656,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -6642,7 +6684,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -6670,7 +6712,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -6698,7 +6740,7 @@
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -6726,7 +6768,7 @@
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>5</v>
       </c>
@@ -6754,7 +6796,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>6</v>
       </c>
@@ -6782,7 +6824,7 @@
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -6810,21 +6852,21 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:9" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="77" t="s">
+    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:9" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="78"/>
-      <c r="E11" s="79"/>
+      <c r="B11" s="79"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="79"/>
+      <c r="E11" s="80"/>
       <c r="G11" s="19">
         <f>SUM(E3:E9)</f>
         <v>17873.480000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="17"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -6832,20 +6874,20 @@
       <c r="E12" s="17"/>
       <c r="G12" s="20"/>
     </row>
-    <row r="13" spans="1:9" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="77" t="s">
+    <row r="13" spans="1:9" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="78"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="78"/>
-      <c r="E13" s="79"/>
+      <c r="B13" s="79"/>
+      <c r="C13" s="79"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="80"/>
       <c r="G13" s="21">
         <f>SUM(G3:G9)</f>
         <v>1456152.4156000002</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="17"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -6853,20 +6895,20 @@
       <c r="E14" s="17"/>
       <c r="G14" s="20"/>
     </row>
-    <row r="15" spans="1:9" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="77" t="s">
+    <row r="15" spans="1:9" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="78"/>
-      <c r="C15" s="78"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="79"/>
+      <c r="B15" s="79"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="79"/>
+      <c r="E15" s="80"/>
       <c r="G15" s="21">
         <f>AVERAGE(G3:G9)</f>
         <v>208021.77365714288</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -6874,20 +6916,20 @@
       <c r="E16" s="17"/>
       <c r="G16" s="20"/>
     </row>
-    <row r="17" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="77" t="s">
+    <row r="17" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="79"/>
+      <c r="B17" s="79"/>
+      <c r="C17" s="79"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="80"/>
       <c r="G17" s="21">
         <f>MAX(G3:G9)</f>
         <v>993934</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="17"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -6895,20 +6937,20 @@
       <c r="E18" s="17"/>
       <c r="G18" s="20"/>
     </row>
-    <row r="19" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="77" t="s">
+    <row r="19" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="78"/>
-      <c r="C19" s="78"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="79"/>
+      <c r="B19" s="79"/>
+      <c r="C19" s="79"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="80"/>
       <c r="G19" s="19">
         <f>MAX(E3:E9)</f>
         <v>12200</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
@@ -6916,19 +6958,19 @@
       <c r="E20" s="17"/>
       <c r="G20" s="22"/>
     </row>
-    <row r="21" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="77" t="s">
+    <row r="21" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="78"/>
-      <c r="C21" s="78"/>
-      <c r="D21" s="78"/>
-      <c r="E21" s="79"/>
+      <c r="B21" s="79"/>
+      <c r="C21" s="79"/>
+      <c r="D21" s="79"/>
+      <c r="E21" s="80"/>
       <c r="G21" s="23">
         <v>81.47</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A19:E19"/>
@@ -6952,9 +6994,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A59E699E-EAE9-447F-8DF7-9DBB5A34244F}">
   <dimension ref="A1:AY3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
         <v>21</v>
       </c>
@@ -6969,7 +7011,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>23</v>
       </c>
@@ -7162,7 +7204,7 @@
       <c r="AX2" s="24"/>
       <c r="AY2" s="24"/>
     </row>
-    <row r="3" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>24</v>
       </c>
@@ -7360,12 +7402,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9E7F91E-FD1D-4626-A187-F1006800E00C}">
   <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="195" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="195" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>25</v>
       </c>
@@ -7398,7 +7440,7 @@
       </c>
       <c r="K1" s="26"/>
     </row>
-    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27">
         <v>1</v>
       </c>
@@ -7410,34 +7452,34 @@
       </c>
       <c r="D2" s="35">
         <f ca="1">RANDBETWEEN(1, 100)</f>
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="E2" s="35">
         <f t="shared" ref="E2:J11" ca="1" si="0">RANDBETWEEN(1, 100)</f>
+        <v>35</v>
+      </c>
+      <c r="F2" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="G2" s="35">
+        <f t="shared" ca="1" si="0"/>
         <v>86</v>
       </c>
-      <c r="F2" s="35">
-        <f t="shared" ca="1" si="0"/>
-        <v>56</v>
-      </c>
-      <c r="G2" s="35">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
       <c r="H2" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I2" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J2" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="27">
         <v>2</v>
       </c>
@@ -7449,34 +7491,34 @@
       </c>
       <c r="D3" s="35">
         <f t="shared" ref="D3:D11" ca="1" si="1">RANDBETWEEN(1, 100)</f>
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="E3" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="F3" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="G3" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="H3" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I3" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J3" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="27">
         <v>3</v>
       </c>
@@ -7488,11 +7530,11 @@
       </c>
       <c r="D4" s="35">
         <f t="shared" ca="1" si="1"/>
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="E4" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F4" s="35">
         <f t="shared" ca="1" si="0"/>
@@ -7500,22 +7542,22 @@
       </c>
       <c r="G4" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="H4" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I4" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="J4" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="27">
         <v>4</v>
       </c>
@@ -7527,34 +7569,34 @@
       </c>
       <c r="D5" s="35">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="E5" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F5" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G5" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="H5" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="I5" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="J5" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>56</v>
+        <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="27">
         <v>5</v>
       </c>
@@ -7566,34 +7608,34 @@
       </c>
       <c r="D6" s="35">
         <f t="shared" ca="1" si="1"/>
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="E6" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="F6" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="G6" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H6" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="I6" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="J6" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="27">
         <v>6</v>
       </c>
@@ -7605,19 +7647,19 @@
       </c>
       <c r="D7" s="35">
         <f t="shared" ca="1" si="1"/>
-        <v>87</v>
+        <v>6</v>
       </c>
       <c r="E7" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F7" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="G7" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="H7" s="35">
         <f t="shared" ca="1" si="0"/>
@@ -7625,14 +7667,14 @@
       </c>
       <c r="I7" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="27">
         <v>7</v>
       </c>
@@ -7644,34 +7686,34 @@
       </c>
       <c r="D8" s="35">
         <f t="shared" ca="1" si="1"/>
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="E8" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="G8" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="H8" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="I8" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="J8" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="27">
         <v>8</v>
       </c>
@@ -7683,34 +7725,34 @@
       </c>
       <c r="D9" s="35">
         <f t="shared" ca="1" si="1"/>
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="E9" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="F9" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="G9" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="H9" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="I9" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="J9" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="27">
         <v>9</v>
       </c>
@@ -7722,34 +7764,34 @@
       </c>
       <c r="D10" s="35">
         <f t="shared" ca="1" si="1"/>
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="E10" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="F10" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="G10" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="H10" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="I10" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="29">
         <v>10</v>
       </c>
@@ -7761,47 +7803,47 @@
       </c>
       <c r="D11" s="37">
         <f t="shared" ca="1" si="1"/>
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="E11" s="37">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="F11" s="37">
         <f t="shared" ca="1" si="0"/>
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="G11" s="37">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="H11" s="37">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="I11" s="37">
         <f t="shared" ca="1" si="0"/>
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="J11" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:11" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="D2:J11">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="lessThan">
       <formula>51</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThanOrEqual">
       <formula>86</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="between">
       <formula>71</formula>
       <formula>85</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="between">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="between">
       <formula>51</formula>
       <formula>70</formula>
     </cfRule>
@@ -7813,50 +7855,50 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFBA9F6-94BC-40E8-9B8D-9CA5711B3D2D}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="40">
         <f ca="1">TODAY()</f>
         <v>45985</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="18">
         <f ca="1">YEAR(TODAY())</f>
         <v>2025</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="18">
         <f ca="1">DAY(TODAY())</f>
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="str">
         <f ca="1">TEXT(TODAY(),"ДДДД")</f>
         <v>понедельник</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="40">
         <v>39542</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="82">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="77">
         <f ca="1">DATEDIF(A5, A1, "y")</f>
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="40">
         <f ca="1">NOW()</f>
-        <v>45985.393178587961</v>
+        <v>45985.509959606483</v>
       </c>
     </row>
   </sheetData>
@@ -7867,16 +7909,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8778C508-0A5A-4411-A338-F1561AA39531}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="39">
         <f ca="1">NOW()</f>
-        <v>45985.393178587961</v>
+        <v>45985.509959606483</v>
       </c>
       <c r="B1" s="39" t="str">
         <f ca="1" xml:space="preserve"> IF(TIME(13,0,0)&lt;=A1&lt;=TIME(14,0,0),"Обед","Работаем")</f>
@@ -7891,18 +7933,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69F9F9B8-BD7C-4A57-BDEC-33D15D957C09}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="41" t="s">
         <v>1</v>
       </c>
@@ -7925,7 +7967,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="44">
         <v>1</v>
       </c>
@@ -7935,11 +7977,11 @@
       </c>
       <c r="C2" s="46">
         <f t="shared" ref="C2:E11" ca="1" si="0">RANDBETWEEN(2,5)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="46">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2" s="46">
         <f t="shared" ca="1" si="0"/>
@@ -7947,43 +7989,43 @@
       </c>
       <c r="F2" s="46">
         <f ca="1">B2+C2+D2+E2</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G2" s="45" t="str">
         <f ca="1">IF(AND(C2&gt;=4,F2&gt;=$E$12),"да","нет")</f>
         <v>нет</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="44">
         <v>2</v>
       </c>
       <c r="B3" s="46">
         <f t="shared" ref="B3:B11" ca="1" si="1">RANDBETWEEN(2,5)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="46">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" s="46">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3" s="46">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" s="46">
         <f t="shared" ref="F3:F11" ca="1" si="2">B3+C3+D3+E3</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G3" s="45" t="str">
         <f t="shared" ref="G3:G11" ca="1" si="3">IF(AND(C3&gt;=4,F3&gt;=$E$12),"да","нет")</f>
-        <v>нет</v>
+        <v>да</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="44">
         <v>3</v>
       </c>
@@ -7993,26 +8035,26 @@
       </c>
       <c r="C4" s="46">
         <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D4" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E4" s="46">
+        <f t="shared" ca="1" si="0"/>
         <v>2</v>
-      </c>
-      <c r="D4" s="46">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="E4" s="46">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
       </c>
       <c r="F4" s="46">
         <f t="shared" ca="1" si="2"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>нет</v>
+        <v>да</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="44">
         <v>4</v>
       </c>
@@ -8022,32 +8064,32 @@
       </c>
       <c r="C5" s="46">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="46">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E5" s="46">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="46">
         <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G5" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>да</v>
+        <v>нет</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="44">
         <v>5</v>
       </c>
       <c r="B6" s="46">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="46">
         <f t="shared" ca="1" si="0"/>
@@ -8059,47 +8101,47 @@
       </c>
       <c r="E6" s="46">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6" s="46">
         <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>да</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="44">
         <v>6</v>
       </c>
       <c r="B7" s="46">
         <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="C7" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D7" s="46">
+        <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="C7" s="46">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D7" s="46">
+      <c r="E7" s="46">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
-      </c>
-      <c r="E7" s="46">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
       </c>
       <c r="F7" s="46">
         <f t="shared" ca="1" si="2"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G7" s="45" t="str">
         <f ca="1">IF(AND(C7&gt;=4,F7&gt;=$E$12),"да","нет")</f>
         <v>нет</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="44">
         <v>7</v>
       </c>
@@ -8117,24 +8159,24 @@
       </c>
       <c r="E8" s="46">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" s="46">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G8" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>да</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="44">
         <v>8</v>
       </c>
       <c r="B9" s="46">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" s="46">
         <f t="shared" ca="1" si="0"/>
@@ -8146,7 +8188,7 @@
       </c>
       <c r="E9" s="46">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9" s="46">
         <f t="shared" ca="1" si="2"/>
@@ -8157,69 +8199,69 @@
         <v>да</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="44">
         <v>9</v>
       </c>
       <c r="B10" s="46">
         <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="C10" s="46">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="D10" s="46">
+        <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="C10" s="46">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="D10" s="46">
+      <c r="E10" s="46">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
-      </c>
-      <c r="E10" s="46">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
       </c>
       <c r="F10" s="46">
         <f t="shared" ca="1" si="2"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>да</v>
+        <v>нет</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="44">
         <v>10</v>
       </c>
       <c r="B11" s="46">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" s="46">
         <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D11" s="46">
+        <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="D11" s="46">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
       <c r="E11" s="46">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F11" s="46">
         <f t="shared" ca="1" si="2"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G11" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>нет</v>
+        <v>да</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="81" t="s">
+    <row r="12" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C12" s="82" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="81"/>
+      <c r="D12" s="82"/>
       <c r="E12" s="41">
         <v>13</v>
       </c>
@@ -8236,20 +8278,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4160CBED-B335-4E19-9D48-D672E35BACD3}">
   <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
-    <col min="4" max="4" width="23.7109375" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.88671875" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="35.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="47" t="s">
         <v>25</v>
       </c>
@@ -8270,7 +8312,7 @@
       </c>
       <c r="H1" s="64"/>
     </row>
-    <row r="2" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="47">
         <v>1</v>
       </c>
@@ -8299,7 +8341,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="50">
         <v>2</v>
       </c>
@@ -8329,7 +8371,7 @@
         <v>27160.716</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="50">
         <v>3</v>
       </c>
@@ -8359,7 +8401,7 @@
         <v>17284.092000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="47">
         <v>4</v>
       </c>
@@ -8389,7 +8431,7 @@
         <v>17284.092000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="50">
         <v>5</v>
       </c>
@@ -8419,7 +8461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="50">
         <v>6</v>
       </c>
@@ -8442,7 +8484,7 @@
         <v>7407.4679999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="47">
         <v>7</v>
       </c>
@@ -8471,7 +8513,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="50">
         <v>8</v>
       </c>
@@ -8501,7 +8543,7 @@
         <v>32099.028000000006</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="50">
         <v>9</v>
       </c>
@@ -8531,7 +8573,7 @@
         <v>22222.403999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="47">
         <v>10</v>
       </c>
@@ -8561,8 +8603,8 @@
         <v>7407.4679999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="60" t="s">
         <v>68</v>
       </c>
@@ -8574,7 +8616,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="60" t="s">
         <v>69</v>
       </c>
@@ -8586,7 +8628,7 @@
         <v>12345.78</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="60" t="s">
         <v>70</v>
       </c>
